--- a/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/test_DAQE.xlsx
+++ b/DAQEAI_Codebase_Apr2026/datf_core/test/testprotocol/test_DAQE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naveen.natarajan\Downloads\DAQEAI_Codebase_Apr2026\DAQEAI_Codebase_Apr2026\datf_core\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0366D4-B658-440A-B002-8DC013C2E5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBA41EA-901B-49C9-A228-79D1C2645470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
   <si>
     <t>comparetype</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>workspace.learning.sfo_customer_survey_delta_target</t>
+  </si>
+  <si>
+    <t>Source</t>
   </si>
 </sst>
 </file>
@@ -973,7 +976,9 @@
       <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
       </c>
